--- a/20240304_ternary_test/output/20240304_ternary_test_pairs.xlsx
+++ b/20240304_ternary_test/output/20240304_ternary_test_pairs.xlsx
@@ -8,56 +8,56 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ru" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Rh" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ir" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Pr" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-La" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Sm" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Tb" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Nd" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Y" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Ge" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Si" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ho" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Pt" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Tm" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Yb" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Ge" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tm-Ge" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Si" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pt" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Sb" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Yb" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Pt" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Sb" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Pt" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Y" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Si" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Sb" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Pt" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Pt" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Pt" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sm" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-U" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Tb" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Sm" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-U" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Nd" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Pr" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-La" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ni" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ir" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Pt" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ir" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Si" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ir" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ir" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Ge" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ir" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ir" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ir" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ge" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300177.cif</t>
+          <t>300177 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -513,11 +513,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300178.cif</t>
+          <t>300177.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.214</v>
+        <v>2.206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300179.cif</t>
+          <t>300178.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.215</v>
+        <v>2.214</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -543,11 +543,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300182.cif</t>
+          <t>300178 2.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.223</v>
+        <v>2.214</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -558,11 +558,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300180.cif</t>
+          <t>300179.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.224</v>
+        <v>2.215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -573,26 +573,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1040392.cif</t>
+          <t>300179 2.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.226</v>
+        <v>2.215</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300181.cif</t>
+          <t>300182.cif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.227</v>
+        <v>2.223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -603,11 +603,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300182 2.cif</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.233</v>
+        <v>2.223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -618,11 +618,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300164.cif</t>
+          <t>300180.cif</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.236</v>
+        <v>2.224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300166.cif</t>
+          <t>300180 2.cif</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.249</v>
+        <v>2.224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -648,26 +648,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300167.cif</t>
+          <t>1040392.cif</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.255</v>
+        <v>2.226</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>300168.cif</t>
+          <t>300181.cif</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.265</v>
+        <v>2.227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -678,11 +678,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>300172.cif</t>
+          <t>300181 2.cif</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.275</v>
+        <v>2.227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -693,11 +693,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>300170.cif</t>
+          <t>300163.cif</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.28</v>
+        <v>2.233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -708,11 +708,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>300173.cif</t>
+          <t>300163 2.cif</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.289</v>
+        <v>2.233</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>300169.cif</t>
+          <t>300164 2.cif</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.29</v>
+        <v>2.236</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -738,11 +738,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>300156.cif</t>
+          <t>300164.cif</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.304</v>
+        <v>2.236</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -753,11 +753,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>300165.cif</t>
+          <t>300166 2.cif</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.306</v>
+        <v>2.249</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -768,11 +768,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>300176.cif</t>
+          <t>300166.cif</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.307</v>
+        <v>2.249</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>300157.cif</t>
+          <t>300167 2.cif</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.317</v>
+        <v>2.255</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>300167.cif</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.323</v>
+        <v>2.255</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -813,11 +813,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>300168.cif</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.329</v>
+        <v>2.265</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -828,11 +828,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300168 2.cif</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.352</v>
+        <v>2.265</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>300174.cif</t>
+          <t>300172 2.cif</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.359</v>
+        <v>2.275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -858,11 +858,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300172.cif</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.359</v>
+        <v>2.275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -873,11 +873,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>300175.cif</t>
+          <t>300170 2.cif</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.382</v>
+        <v>2.28</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>300171.cif</t>
+          <t>300170.cif</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.383</v>
+        <v>2.28</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -903,11 +903,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>300173 2.cif</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.396</v>
+        <v>2.289</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -918,26 +918,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1005628.cif</t>
+          <t>300173.cif</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.401</v>
+        <v>2.289</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>300352.cif</t>
+          <t>300169.cif</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.438</v>
+        <v>2.29</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -948,13 +948,448 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>300169 2.cif</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>300156 2.cif</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>300165.cif</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.306</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>300165 2.cif</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.306</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>300176 2.cif</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>300176.cif</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>300157 2.cif</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>300158 2.cif</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>300160 2.cif</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>300161 2.cif</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>300174 2.cif</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>300162 2.cif</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>300174.cif</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>300175 2.cif</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>300175.cif</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>300171 2.cif</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>300159 2.cif</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1005628.cif</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>300352.cif</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>300352 2.cif</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>300355.cif</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B60" t="n">
         <v>2.442</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>300355 2.cif</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -971,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,11 +1444,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300236.cif</t>
+          <t>300235 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.717</v>
+        <v>2.71</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1024,13 +1459,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>300236.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300236 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>300237.cif</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>2.727</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300237 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -1047,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,11 +1565,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300236.cif</t>
+          <t>300235 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.717</v>
+        <v>2.71</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1100,13 +1580,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>300236.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300236 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>300237.cif</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>2.727</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300237 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -1123,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,11 +1671,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>300159 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141</v>
+        <v>3.179</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1161,11 +1686,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300203.cif</t>
+          <t>300159.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.198</v>
+        <v>3.179</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1176,13 +1701,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300166.cif</t>
+          <t>300171 2.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.201</v>
+        <v>3.182</v>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300165.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.236</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300165 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.236</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1199,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1222,7 +1792,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>300158 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1237,11 +1807,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300202.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.165</v>
+        <v>3.135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1252,13 +1822,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>300202 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.165</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300202.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.165</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>300163.cif</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>3.187</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300163 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1275,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,11 +1913,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300160 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1313,11 +1928,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300204.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.208</v>
+        <v>3.141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1328,13 +1943,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300167.cif</t>
+          <t>300203.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.21</v>
+        <v>3.198</v>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300203 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300166 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300166.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1351,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,11 +2034,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>300161 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.179</v>
+        <v>3.157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1389,11 +2049,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300171.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.182</v>
+        <v>3.157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1404,13 +2064,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300165.cif</t>
+          <t>300204 2.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.236</v>
+        <v>3.208</v>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300204.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300167 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300167.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1427,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,7 +2155,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300176.cif</t>
+          <t>300176 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1465,13 +2170,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>300176.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.122</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>300182.cif</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>3.188</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300182 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1488,7 +2223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,13 +2261,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>300357 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300361 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>300361.cif</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B5" t="n">
         <v>2.385</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1549,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,13 +2352,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>300157 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>300181.cif</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>3.184</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300181 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.184</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1610,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,11 +2428,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300156.cif</t>
+          <t>300354.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.12</v>
+        <v>2.388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1648,13 +2443,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300180.cif</t>
+          <t>300354 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.18</v>
+        <v>2.388</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300353 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300353.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1671,7 +2496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,7 +2519,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300177.cif</t>
+          <t>300177 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1709,11 +2534,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300178.cif</t>
+          <t>300177.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.493</v>
+        <v>2.491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1724,11 +2549,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300179.cif</t>
+          <t>300178.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.497</v>
+        <v>2.493</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1739,11 +2564,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300180.cif</t>
+          <t>300178 2.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.501</v>
+        <v>2.493</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1754,11 +2579,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300181.cif</t>
+          <t>300179.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.505</v>
+        <v>2.497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1769,11 +2594,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300182.cif</t>
+          <t>300179 2.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.506</v>
+        <v>2.497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1784,11 +2609,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300180.cif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.507</v>
+        <v>2.501</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1799,11 +2624,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300164.cif</t>
+          <t>300180 2.cif</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.513</v>
+        <v>2.501</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1814,11 +2639,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300166.cif</t>
+          <t>300181.cif</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.52</v>
+        <v>2.505</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1829,11 +2654,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300167.cif</t>
+          <t>300181 2.cif</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.527</v>
+        <v>2.505</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1844,11 +2669,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300168.cif</t>
+          <t>300182.cif</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.535</v>
+        <v>2.506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,11 +2684,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>300170.cif</t>
+          <t>300182 2.cif</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.543</v>
+        <v>2.506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,11 +2699,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>300169.cif</t>
+          <t>300163.cif</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.554</v>
+        <v>2.507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1889,13 +2714,223 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>300163 2.cif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>300164 2.cif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.513</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.513</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>300166 2.cif</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>300166.cif</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>300167 2.cif</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.527</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>300167.cif</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.527</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>300168.cif</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>300168 2.cif</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>300170 2.cif</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>300169 2.cif</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>300165.cif</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B28" t="n">
         <v>2.554</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>300165 2.cif</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1912,7 +2947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,11 +2970,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300354.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.388</v>
+        <v>3.12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1950,13 +2985,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300353.cif</t>
+          <t>300156 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.416</v>
+        <v>3.12</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300180.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300180 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1973,7 +3038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1996,11 +3061,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300352.cif</t>
+          <t>300172 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.489</v>
+        <v>3.089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2011,13 +3076,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300355.cif</t>
+          <t>300172.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.499</v>
+        <v>3.089</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300177 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300177.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2034,7 +3129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2057,11 +3152,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300173.cif</t>
+          <t>300352.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.093</v>
+        <v>2.489</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2072,13 +3167,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300178.cif</t>
+          <t>300352 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.171</v>
+        <v>2.489</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300355.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300355 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2095,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,11 +3243,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300172.cif</t>
+          <t>300173 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.089</v>
+        <v>3.093</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2133,13 +3258,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300177.cif</t>
+          <t>300173.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.17</v>
+        <v>3.093</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300178.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.171</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300178 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.171</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2156,7 +3311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2179,7 +3334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300359.cif</t>
+          <t>300359 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2194,13 +3349,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>300359.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300358 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.453</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>300358.cif</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B5" t="n">
         <v>2.453</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2217,7 +3402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,6 +3432,21 @@
         <v>3.14</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300237 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -2263,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2293,6 +3493,21 @@
         <v>3.14</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300237 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -2309,7 +3524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,6 +3554,21 @@
         <v>3.114</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300236 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.114</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -2355,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +3615,21 @@
         <v>3.114</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300236 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.114</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -2401,7 +3646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,13 +3669,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300354.cif</t>
+          <t>300351 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.143</v>
+        <v>2.242</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300351.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2447,7 +3707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,7 +3730,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300172.cif</t>
+          <t>300172 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2485,11 +3745,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300173.cif</t>
+          <t>300172.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.46</v>
+        <v>2.455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2500,11 +3760,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300156.cif</t>
+          <t>300173 2.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.481</v>
+        <v>2.46</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2515,11 +3775,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300176.cif</t>
+          <t>300173.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.483</v>
+        <v>2.46</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2530,11 +3790,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300157.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.487</v>
+        <v>2.481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2545,11 +3805,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>300156 2.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.495</v>
+        <v>2.481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2560,11 +3820,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>300176 2.cif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.499</v>
+        <v>2.483</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2575,11 +3835,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300176.cif</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.515</v>
+        <v>2.483</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2590,11 +3850,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300157.cif</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.519</v>
+        <v>2.487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2605,11 +3865,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300174.cif</t>
+          <t>300157 2.cif</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.524</v>
+        <v>2.487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2620,11 +3880,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>300158 2.cif</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.538</v>
+        <v>2.495</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2635,13 +3895,193 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>300160 2.cif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>300161 2.cif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>300162 2.cif</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>300174 2.cif</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>300174.cif</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>300159 2.cif</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>300175 2.cif</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>300175.cif</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B25" t="n">
         <v>2.542</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2658,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2681,15 +4121,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300235.cif</t>
+          <t>300351 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.089</v>
+        <v>2.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300351.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -2704,7 +4159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2727,15 +4182,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300235.cif</t>
+          <t>300351 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.089</v>
+        <v>2.385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300351.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -2750,7 +4220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,13 +4243,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300355.cif</t>
+          <t>300354.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.274</v>
+        <v>3.143</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300354 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2796,7 +4281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2819,15 +4304,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300351.cif</t>
+          <t>300235.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.242</v>
+        <v>3.089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300235 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.089</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -2842,7 +4342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2865,15 +4365,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300351.cif</t>
+          <t>300235.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.385</v>
+        <v>3.089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300235 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.089</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -2888,7 +4403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2911,13 +4426,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300351.cif</t>
+          <t>300355.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.99</v>
+        <v>3.274</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300355 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.274</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2934,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2964,6 +4494,21 @@
         <v>3.263</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300352 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -2980,7 +4525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3010,6 +4555,21 @@
         <v>3.177</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300179 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3026,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3056,6 +4616,21 @@
         <v>2.838</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300245 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3072,7 +4647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3095,13 +4670,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300362.cif</t>
+          <t>300202 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.227</v>
+        <v>3.282</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300202.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.282</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3118,7 +4708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3141,11 +4731,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300362.cif</t>
+          <t>300202 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.455</v>
+        <v>2.348</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3160,7 +4750,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.473</v>
+        <v>2.348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3175,7 +4765,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.488</v>
+        <v>2.367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3186,11 +4776,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300204.cif</t>
+          <t>300203 2.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.492</v>
+        <v>2.367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3201,11 +4791,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300205.cif</t>
+          <t>300204 2.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.499</v>
+        <v>2.373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3216,11 +4806,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300206.cif</t>
+          <t>300204.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.507</v>
+        <v>2.373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3231,11 +4821,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300207.cif</t>
+          <t>300205.cif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.521</v>
+        <v>2.38</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3246,13 +4836,133 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>300205 2.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300206 2.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.387</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300206.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.387</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300207 2.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>300207.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>300362.cif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>300362 2.cif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>300171 2.cif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>300171.cif</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B17" t="n">
         <v>2.537</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3269,7 +4979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,13 +5002,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300202.cif</t>
+          <t>300358 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.282</v>
+        <v>3.244</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300358.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.244</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3315,7 +5040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3338,13 +5063,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300203.cif</t>
+          <t>300361 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.274</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300361.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.141</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3361,7 +5101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3384,13 +5124,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300361.cif</t>
+          <t>300204 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141</v>
+        <v>3.27</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300204.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3407,7 +5162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3430,13 +5185,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300358.cif</t>
+          <t>300164 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.244</v>
+        <v>3.194</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3453,7 +5223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3476,13 +5246,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300204.cif</t>
+          <t>300206 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.27</v>
+        <v>3.291</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300206.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3499,7 +5284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,13 +5307,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300205.cif</t>
+          <t>300362.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.279</v>
+        <v>3.227</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300362 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3545,7 +5345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3568,13 +5368,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300207.cif</t>
+          <t>300203.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.306</v>
+        <v>3.274</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300203 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.274</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3591,7 +5406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,15 +5429,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1040392.cif</t>
+          <t>300205.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.477</v>
+        <v>3.279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300205 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.279</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -3637,7 +5467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3660,15 +5490,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1040392.cif</t>
+          <t>300207 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.226</v>
+        <v>3.306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300207.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.306</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -3710,7 +5555,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141</v>
+        <v>2.226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3729,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3767,11 +5612,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300236.cif</t>
+          <t>300235 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.717</v>
+        <v>2.71</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3782,11 +5627,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300237.cif</t>
+          <t>300236.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>2.717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3797,13 +5642,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>300236 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300237 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>300245.cif</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B8" t="n">
         <v>2.838</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300245 2.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -3843,15 +5748,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300206.cif</t>
+          <t>1040392.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.291</v>
+        <v>2.226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency</t>
         </is>
       </c>
     </row>
@@ -3889,15 +5794,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300164.cif</t>
+          <t>1040392.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.194</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency</t>
         </is>
       </c>
     </row>
@@ -3912,7 +5817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3935,7 +5840,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300162 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3950,43 +5855,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1005628.cif</t>
+          <t>300162.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.168</v>
+        <v>3.161</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300205.cif</t>
+          <t>1005628.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.217</v>
+        <v>3.168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>300205.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.217</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300205 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.217</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>300168.cif</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
         <v>3.22</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300168 2.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -4003,7 +5953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4041,7 +5991,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300174.cif</t>
+          <t>300174 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4056,11 +6006,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300206.cif</t>
+          <t>300174.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.226</v>
+        <v>3.169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4071,13 +6021,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>300206 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.226</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300206.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.226</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300170 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>300170.cif</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B8" t="n">
         <v>3.227</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -4094,7 +6089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4117,7 +6112,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300175.cif</t>
+          <t>300175 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4132,11 +6127,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300169.cif</t>
+          <t>300175.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.241</v>
+        <v>3.189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4147,13 +6142,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300169 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300207 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.246</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>300207.cif</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B7" t="n">
         <v>3.246</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -4170,7 +6210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4208,11 +6248,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300353.cif</t>
+          <t>300357 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.185</v>
+        <v>3.131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4223,13 +6263,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>300353 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.185</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300353.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.185</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300359 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>300359.cif</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B7" t="n">
         <v>3.201</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
